--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeong-uchan/Desktop/myLife/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B3E642-EF4D-AE49-8CEC-12F679F988EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA37934F-B2CE-134A-B098-3509AB685733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -1000,9 +1000,6 @@
       <c r="A33" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E33">
-        <v>67</v>
-      </c>
       <c r="G33"/>
     </row>
     <row r="34" spans="1:12">
@@ -1010,10 +1007,10 @@
         <v>54</v>
       </c>
       <c r="E34">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F34">
-        <v>48962</v>
+        <v>82640</v>
       </c>
       <c r="G34"/>
     </row>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeong-uchan/Desktop/myLife/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA37934F-B2CE-134A-B098-3509AB685733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709E5D6B-B2B6-A144-AAA0-B5008106E773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
+    <workbookView xWindow="2420" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeong-uchan/Desktop/myLife/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709E5D6B-B2B6-A144-AAA0-B5008106E773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FBD39E-8439-A549-8253-AF000CA72939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="86">
   <si>
     <t>spendMoney</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -348,6 +348,10 @@
   </si>
   <si>
     <t>2025.4.22</t>
+  </si>
+  <si>
+    <t>9:56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1000,6 +1004,18 @@
       <c r="A33" s="5" t="s">
         <v>53</v>
       </c>
+      <c r="B33">
+        <v>1.73</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33">
+        <v>70</v>
+      </c>
+      <c r="F33">
+        <v>9800</v>
+      </c>
       <c r="G33"/>
     </row>
     <row r="34" spans="1:12">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeong-uchan/Desktop/myLife/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FBD39E-8439-A549-8253-AF000CA72939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CDA13D-AD85-EB4C-A775-8A9726F66461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1014,7 +1014,7 @@
         <v>70</v>
       </c>
       <c r="F33">
-        <v>9800</v>
+        <v>18012</v>
       </c>
       <c r="G33"/>
     </row>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeong-uchan/Desktop/myLife/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CDA13D-AD85-EB4C-A775-8A9726F66461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33800F6A-4A51-7C47-BE5C-F00D49EC7A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
   <si>
     <t>spendMoney</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -351,6 +351,10 @@
   </si>
   <si>
     <t>9:56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3:2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -782,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8D4A88-66D6-9248-999B-92DF8B428426}">
-  <dimension ref="A1:L132"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="5" bestFit="1" customWidth="1"/>
@@ -904,124 +908,130 @@
       </c>
       <c r="G16"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:15">
       <c r="A17" s="5" t="s">
         <v>63</v>
       </c>
       <c r="G17"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:15">
       <c r="A18" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:15">
       <c r="A19" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:15">
       <c r="A20" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:15">
       <c r="A21" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:15">
       <c r="A22" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G22"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:15">
       <c r="A23" s="5" t="s">
         <v>69</v>
       </c>
       <c r="G23"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:15">
       <c r="A24" s="5" t="s">
         <v>70</v>
       </c>
       <c r="G24"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:15">
       <c r="A25" s="5" t="s">
         <v>71</v>
       </c>
       <c r="G25"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:15">
       <c r="A26" s="5" t="s">
         <v>72</v>
       </c>
       <c r="G26"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:15">
       <c r="A27" s="5" t="s">
         <v>73</v>
       </c>
       <c r="G27"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:15">
       <c r="A28" s="5" t="s">
         <v>74</v>
       </c>
       <c r="G28"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:15">
       <c r="A29" s="5" t="s">
         <v>75</v>
       </c>
       <c r="G29"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:15">
       <c r="A30" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G30"/>
     </row>
-    <row r="31" spans="1:7" s="7" customFormat="1">
+    <row r="31" spans="1:15" s="7" customFormat="1">
       <c r="A31" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:15">
       <c r="A32" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D32" s="3"/>
       <c r="G32"/>
+      <c r="K32">
+        <v>1.73</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N32">
+        <v>70</v>
+      </c>
+      <c r="O32">
+        <v>18012</v>
+      </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B33">
-        <v>1.73</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33">
-        <v>70</v>
-      </c>
-      <c r="F33">
-        <v>18012</v>
-      </c>
       <c r="G33"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="5" t="s">
         <v>54</v>
       </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="E34">
         <v>100</v>
       </c>
@@ -1033,6 +1043,12 @@
     <row r="35" spans="1:12">
       <c r="A35" s="5" t="s">
         <v>55</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="E35">
         <v>41</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeong-uchan/Desktop/myLife/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33800F6A-4A51-7C47-BE5C-F00D49EC7A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55F61C9-B273-1B4F-AB83-E210C1D1CD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{D3448A19-EE9A-D84F-AF10-A95129378CE2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
   <si>
     <t>spendMoney</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -351,10 +351,9 @@
   </si>
   <si>
     <t>9:56</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3:2</t>
+  </si>
+  <si>
+    <t>9:56</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -427,7 +426,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -451,6 +450,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1007,7 +1009,7 @@
         <v>1.73</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N32">
         <v>70</v>
@@ -1020,18 +1022,25 @@
       <c r="A33" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G33"/>
+      <c r="B33" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1">
+        <v>70</v>
+      </c>
+      <c r="F33" s="1">
+        <v>18012</v>
+      </c>
+      <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E34">
         <v>100</v>
       </c>
@@ -1043,12 +1052,6 @@
     <row r="35" spans="1:12">
       <c r="A35" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E35">
         <v>41</v>
